--- a/documentos_terminados/RA_Gecko.xlsx
+++ b/documentos_terminados/RA_Gecko.xlsx
@@ -6435,7 +6435,7 @@
       <c r="C3" s="127"/>
       <c r="D3" s="52" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/09/2026</t>
+          <t xml:space="preserve">29/09/2026</t>
         </is>
       </c>
       <c r="E3" s="143" t="s">
@@ -7287,24 +7287,80 @@
       <c r="S15" s="57"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación normal - verificación Poka Yoke de presencia/orientación de la pieza</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada antes de permitir el ciclo; el operador puede tener contacto accidental con el mecanismo al cargar la pieza</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J16" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K16" s="107"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="49"/>
+      <c r="K16" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No se requiere EPP adicional.</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+        </is>
+      </c>
+      <c r="N16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P16" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7317,24 +7373,80 @@
       <c r="S16" s="57"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación normal - lectura de código con escáner fijo</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo; el operador puede golpearse con el brazo/soporte del escáner al cargar o descargar material</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J17" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="107"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="49"/>
+      <c r="K17" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No se requiere EPP adicional.</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+        </is>
+      </c>
+      <c r="N17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P17" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7347,24 +7459,80 @@
       <c r="S17" s="57"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="55"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación normal - contacto con partes fijas de la fixtura (bordes/topes)</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador puede golpearse o atraparse los dedos con los bordes/topes fijos de la fixtura al colocar o retirar la pieza, independientemente de los 2 clamps móviles</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
       <c r="J18" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="49"/>
+      <c r="K18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No se requiere EPP adicional.</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+        </is>
+      </c>
+      <c r="N18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P18" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7377,24 +7545,80 @@
       <c r="S18" s="57"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="55"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación normal - islas de conexión eléctrica (alimentación y sensores)</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las islas/bloques de conexión eléctrica de alimentación y de sensores quedan accesibles en el área de trabajo durante la operación normal</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J19" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="107"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="49"/>
+      <c r="K19" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detección de voltaje</t>
+        </is>
+      </c>
+      <c r="L19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No se requiere EPP adicional; conexiones con guarda de protección, verificar que no presenten aberturas ni cables expuestos.</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+        </is>
+      </c>
+      <c r="N19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P19" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
